--- a/data/Traderes_data.xlsx
+++ b/data/Traderes_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\toolbox-amiris-emlab\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5877BBAB-27AF-489F-A13F-6F49FEABDA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB3E8C93-6462-43A1-B7B0-3E976509DC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6375" yWindow="3015" windowWidth="21600" windowHeight="12735" tabRatio="785" activeTab="5" xr2:uid="{9A6D5CBA-73A9-44EC-81CD-5563DD7C030A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="785" activeTab="5" xr2:uid="{9A6D5CBA-73A9-44EC-81CD-5563DD7C030A}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="12" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="101">
   <si>
     <t>OCGT</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>&lt; these are being overwritten</t>
+  </si>
+  <si>
+    <t>old value</t>
   </si>
 </sst>
 </file>
@@ -3347,15 +3350,17 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49062442-D143-42F9-B57C-0195CD17CFC1}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="21.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.140625" style="27"/>
-    <col min="5" max="16384" width="9.140625" style="1"/>
+    <col min="5" max="9" width="9.140625" style="1"/>
+    <col min="10" max="10" width="13.85546875" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>64</v>
       </c>
@@ -3381,7 +3386,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>20</v>
       </c>
@@ -3394,12 +3399,12 @@
       </c>
       <c r="D2" s="26"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="3">
-        <f t="shared" ref="B3:B7" si="0">C3</f>
+        <f t="shared" ref="B3:B6" si="0">C3</f>
         <v>8.93</v>
       </c>
       <c r="C3" s="28">
@@ -3407,7 +3412,7 @@
       </c>
       <c r="D3" s="26"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
@@ -3420,7 +3425,7 @@
       </c>
       <c r="D4" s="26"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>17</v>
       </c>
@@ -3435,7 +3440,7 @@
         <v>1.69</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>67</v>
       </c>
@@ -3448,7 +3453,7 @@
       </c>
       <c r="D6" s="26"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
@@ -3459,8 +3464,11 @@
       <c r="D7" s="28">
         <v>50.29</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N7" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>14</v>
       </c>
@@ -3487,8 +3495,12 @@
       <c r="L8" s="1" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="N8" s="27">
+        <f>45*33.6/1000</f>
+        <v>1.512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>12</v>
       </c>
@@ -3507,7 +3519,7 @@
         <v>45.07</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>11</v>
       </c>
@@ -3533,7 +3545,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
@@ -3547,7 +3559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>83</v>
       </c>
